--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0750140-4C2A-43EC-8676-FC4B89CFCA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7B33BA-5BD3-4722-9890-43422AD14F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="112">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -345,6 +345,21 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/A5sHoMOAH3dpxK0zv3IoUDxRKn3.jpg</t>
+  </si>
+  <si>
+    <t>Bad Dog</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/de0F1jzlL5KUsia00HHXYOBe3oH.jpg</t>
+  </si>
+  <si>
+    <t>Liv og Død</t>
+  </si>
+  <si>
+    <t>TV3 Puls</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/bsHAdtWQFBYmEU62hdh8f0wn9mw.jpg</t>
   </si>
 </sst>
 </file>
@@ -996,6 +1011,17 @@
         <v>24</v>
       </c>
     </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
@@ -1027,6 +1053,17 @@
       </c>
       <c r="C28" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7B33BA-5BD3-4722-9890-43422AD14F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C27EEA9-44FF-4580-BD61-A8B1FC940414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="115">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -360,6 +360,15 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/bsHAdtWQFBYmEU62hdh8f0wn9mw.jpg</t>
+  </si>
+  <si>
+    <t>Rovdur</t>
+  </si>
+  <si>
+    <t>Lion</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/txDuVTIqvQRhHF83qbxpXgrWxJu.jpg</t>
   </si>
 </sst>
 </file>
@@ -1066,6 +1075,17 @@
         <v>111</v>
       </c>
     </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>55</v>
@@ -1144,7 +1164,15 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C38" s="4"/>
+      <c r="A38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C27EEA9-44FF-4580-BD61-A8B1FC940414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5846A2BF-F46C-4578-91A3-460282BBE83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="117">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/txDuVTIqvQRhHF83qbxpXgrWxJu.jpg</t>
+  </si>
+  <si>
+    <t>Stillehavet</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/84UQWXDEyryznA7Mtyc08FE7ByS.jpg</t>
   </si>
 </sst>
 </file>
@@ -744,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1205,6 +1211,17 @@
       </c>
       <c r="C41" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5846A2BF-F46C-4578-91A3-460282BBE83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8713B084-81E1-45C1-9D40-C68690A99231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="116">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -360,9 +360,6 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/bsHAdtWQFBYmEU62hdh8f0wn9mw.jpg</t>
-  </si>
-  <si>
-    <t>Rovdur</t>
   </si>
   <si>
     <t>Lion</t>
@@ -1083,7 +1080,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -1171,13 +1168,13 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
         <v>56</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1215,13 +1212,13 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8713B084-81E1-45C1-9D40-C68690A99231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D18FA4-5CEE-4BF9-9C55-C1749E1379A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="129">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -372,6 +372,45 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/84UQWXDEyryznA7Mtyc08FE7ByS.jpg</t>
+  </si>
+  <si>
+    <t>Deja-vu med Frøkjær</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/kUDftpP8iTayeJap5vBAekbwyRm.jpg</t>
+  </si>
+  <si>
+    <t>dyreværnet – bag facaden</t>
+  </si>
+  <si>
+    <t>TV3</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/zlAJRIEaVdEdseIdtl726ESxZ01.jpg</t>
+  </si>
+  <si>
+    <t>Herlige haver</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/dcrTDXawCGcyCbywN3ylZEiPWZ8.jpg</t>
+  </si>
+  <si>
+    <t>Sunday - VM Special</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/25HktNJ9lRHQOR2waKHe6s1xGV3.jpg</t>
+  </si>
+  <si>
+    <t>Til salg i 100 år</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/1EcqdGAnHPc9MUMoa03kl2PVzHL.jpg</t>
+  </si>
+  <si>
+    <t>Troldspejlet</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/4QTiNyJfTKTo28551yG5AhWx5TT.jpg</t>
   </si>
 </sst>
 </file>
@@ -747,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1219,6 +1258,83 @@
       </c>
       <c r="C42" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D18FA4-5CEE-4BF9-9C55-C1749E1379A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A7C5CE-D366-47BF-A78C-A1B05E2773D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A7C5CE-D366-47BF-A78C-A1B05E2773D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0770CF74-00F3-4F77-8CEB-54ADD43A7EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -411,6 +411,18 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/4QTiNyJfTKTo28551yG5AhWx5TT.jpg</t>
+  </si>
+  <si>
+    <t>The Dark</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/hCIoLKyCyy9wQpx2fmpGa4nBPC4.jpg</t>
+  </si>
+  <si>
+    <t>Crisis</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/bDxmmwOoTN02iYFNpRGuzdvVRnK.jpg</t>
   </si>
 </sst>
 </file>
@@ -786,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1335,6 +1347,28 @@
       </c>
       <c r="C49" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
